--- a/public/post/2022_01_08_scpa_jc/Schedule.xlsx
+++ b/public/post/2022_01_08_scpa_jc/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xiaotaoshen/github/scpa/content/post/2022_01_08_scpa_jc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E74396A-DB8F-D24C-8DDC-82B9B762FEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1AD16E-C7BF-5E4E-AC7D-5E0B67A50C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{998E4D96-DBC7-A140-8B86-2BDD4638C79D}"/>
   </bookViews>
@@ -219,11 +219,6 @@
     <t>Multiomics in Exposome</t>
   </si>
   <si>
-    <t>Correlative three-dimensional super-resolution
-and block-face electron microscopy of whole
-vitreously frozen cells</t>
-  </si>
-  <si>
     <t>Biological exposome</t>
   </si>
   <si>
@@ -291,6 +286,9 @@
   </si>
   <si>
     <t>Presentation title</t>
+  </si>
+  <si>
+    <t>Correlative three-dimensional super-resolution and block-face electron microscopy of whole vitreously frozen cells</t>
   </si>
 </sst>
 </file>
@@ -680,16 +678,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" t="s">
         <v>81</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>82</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>83</v>
-      </c>
-      <c r="D1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -700,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
         <v>0</v>
@@ -714,7 +712,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -728,7 +726,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -742,7 +740,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -756,7 +754,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
@@ -770,10 +768,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -784,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -798,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>53</v>
@@ -812,7 +810,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -826,7 +824,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>16</v>
@@ -840,7 +838,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -854,7 +852,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>19</v>
@@ -868,7 +866,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>52</v>
@@ -882,10 +880,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -896,13 +894,13 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>44092</v>
       </c>
@@ -910,10 +908,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -924,7 +922,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -935,7 +933,7 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
@@ -949,7 +947,7 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -960,7 +958,7 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -971,10 +969,10 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -985,7 +983,7 @@
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -996,10 +994,10 @@
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -1010,10 +1008,10 @@
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1024,7 +1022,7 @@
         <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1035,7 +1033,7 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -1046,7 +1044,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
         <v>58</v>
@@ -1060,7 +1058,7 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
         <v>57</v>
@@ -1074,10 +1072,10 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -1088,7 +1086,7 @@
         <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
         <v>55</v>
@@ -1102,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
         <v>48</v>
@@ -1116,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
         <v>56</v>
@@ -1130,7 +1128,7 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
         <v>60</v>
@@ -1144,7 +1142,7 @@
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>27</v>
@@ -1158,7 +1156,7 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
         <v>54</v>
@@ -1172,7 +1170,7 @@
         <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
@@ -1186,7 +1184,7 @@
         <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
         <v>31</v>
@@ -1200,7 +1198,7 @@
         <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
         <v>51</v>
@@ -1214,7 +1212,7 @@
         <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
         <v>32</v>
@@ -1239,7 +1237,7 @@
         <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
         <v>36</v>
@@ -1253,7 +1251,7 @@
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D43" t="s">
         <v>37</v>
@@ -1267,7 +1265,7 @@
         <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
@@ -1281,7 +1279,7 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" t="s">
         <v>50</v>
@@ -1295,7 +1293,7 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
         <v>41</v>
@@ -1309,7 +1307,7 @@
         <v>43</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
         <v>42</v>
@@ -1323,7 +1321,7 @@
         <v>44</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" t="s">
         <v>45</v>
@@ -1337,7 +1335,7 @@
         <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
         <v>47</v>
